--- a/assets/forms/repair-form-template.xlsx
+++ b/assets/forms/repair-form-template.xlsx
@@ -203,7 +203,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,6 +285,19 @@
       <color rgb="FF1F3864"/>
       <name val="Angsana New"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -954,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1340,6 +1353,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1716,7 +1735,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.375" style="1" bestFit="1" customWidth="1"/>
@@ -1737,7 +1756,7 @@
       <c r="E1" s="112"/>
       <c r="F1" s="113"/>
     </row>
-    <row r="2" spans="1:9" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A2" s="95" t="s">
         <v>0</v>
       </c>
@@ -1746,8 +1765,13 @@
       <c r="D2" s="96"/>
       <c r="E2" s="96"/>
       <c r="F2" s="97"/>
-    </row>
-    <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="K2" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A3" s="114" t="s">
         <v>32</v>
       </c>
@@ -1758,8 +1782,13 @@
       </c>
       <c r="E3" s="117"/>
       <c r="F3" s="38"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="K3" s="139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="109" t="s">
         <v>33</v>
       </c>
@@ -1770,8 +1799,13 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="27"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="K4" s="139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="109" t="s">
         <v>34</v>
       </c>
@@ -1782,6 +1816,11 @@
       </c>
       <c r="E5" s="69"/>
       <c r="F5" s="27"/>
+      <c r="K5" s="139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="70" t="s">
@@ -2211,7 +2250,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7414DAC3-4EE8-4239-A8F1-85F6B28A0685}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.625" style="9" customWidth="1"/>
@@ -2238,7 +2277,7 @@
       <c r="I1" s="129"/>
       <c r="J1" s="130"/>
     </row>
-    <row r="2" spans="1:10" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="131" t="s">
         <v>32</v>
       </c>
@@ -2257,8 +2296,13 @@
       </c>
       <c r="I2" s="134"/>
       <c r="J2" s="135"/>
-    </row>
-    <row r="3" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="L2" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A3" s="15"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -2269,8 +2313,13 @@
       <c r="H3" s="16"/>
       <c r="I3" s="16"/>
       <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="15"/>
       <c r="B4" s="121" t="s">
         <v>44</v>
@@ -2286,8 +2335,13 @@
       </c>
       <c r="I4" s="127"/>
       <c r="J4" s="17"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="15"/>
       <c r="B5" s="123"/>
       <c r="C5" s="124"/>
@@ -2297,6 +2351,11 @@
       <c r="H5" s="127"/>
       <c r="I5" s="127"/>
       <c r="J5" s="17"/>
+      <c r="L5" s="139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>

--- a/assets/forms/repair-form-template.xlsx
+++ b/assets/forms/repair-form-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Equipment\Air\เอกสารแบบฟอร์มซ่อม ล้าง\ฟอร์ม 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Aircon-manager\assets\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67192793-7B9D-4F65-B398-54058BA13874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3EDA39-6E6D-4E63-BC0C-D66AAD29A636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ใบแจ้งซ่อม" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
   <si>
     <t>ส่วนที่ 1 : ข้อมูล Node และเครื่อง / Node &amp; Unit Information</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t>รูปถ่ายประกอบการซ่อมเครื่องปรับอากาศ</t>
+  </si>
+  <si>
+    <t>วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+  </si>
+  <si>
+    <t>1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+  </si>
+  <si>
+    <t>2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+  </si>
+  <si>
+    <t>3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
   </si>
 </sst>
 </file>
@@ -300,7 +312,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,12 +329,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFF7F9FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7F9FC"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -967,68 +973,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1043,125 +1043,143 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1171,10 +1189,13 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1225,144 +1246,130 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1736,215 +1743,207 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="4.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.75" style="1" customWidth="1"/>
-    <col min="4" max="5" width="9.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.75" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.625" style="1"/>
+    <col min="1" max="1" width="4.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7265625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="9.08984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7265625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="56.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="111" t="s">
+    <row r="1" spans="1:11" ht="56.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="113"/>
-    </row>
-    <row r="2" spans="1:11" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A2" s="95" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="52"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
-      <c r="K2" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="114" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
+      <c r="K2" s="48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="116" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="38"/>
-      <c r="K3" s="139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A4" s="109" t="s">
+      <c r="E3" s="59"/>
+      <c r="F3" s="36"/>
+      <c r="K3" s="49" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="110"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="66" t="s">
+      <c r="B4" s="65"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="67"/>
-      <c r="F4" s="27"/>
-      <c r="K4" s="139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A5" s="109" t="s">
+      <c r="E4" s="73"/>
+      <c r="F4" s="25"/>
+      <c r="K4" s="49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="110"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="68" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="27"/>
-      <c r="K5" s="139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="70" t="s">
+      <c r="E5" s="75"/>
+      <c r="F5" s="25"/>
+      <c r="K5" s="49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="107" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="108"/>
-      <c r="F6" s="26"/>
-    </row>
-    <row r="7" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="70" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="24"/>
+    </row>
+    <row r="7" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="72" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="73"/>
-      <c r="F7" s="26"/>
-    </row>
-    <row r="8" spans="1:9" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A8" s="95" t="s">
+      <c r="E7" s="77"/>
+      <c r="F7" s="24"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="97"/>
-    </row>
-    <row r="9" spans="1:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="54" t="s">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="55"/>
+    </row>
+    <row r="9" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="56"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="57"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="59"/>
-    </row>
-    <row r="11" spans="1:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="57" t="s">
+      <c r="B9" s="106"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="107"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="108"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="109"/>
+      <c r="D10" s="109"/>
+      <c r="E10" s="109"/>
+      <c r="F10" s="110"/>
+    </row>
+    <row r="11" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="59"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="109"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="110"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="57"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="59"/>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="108"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="109"/>
+      <c r="D12" s="109"/>
+      <c r="E12" s="109"/>
+      <c r="F12" s="110"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="57" t="s">
+    <row r="13" spans="1:11" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="59"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="110"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A14" s="104"/>
-      <c r="B14" s="105"/>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="106"/>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="115"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="117"/>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A15" s="95" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="96"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="97"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="55"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="49" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="103"/>
+      <c r="C16" s="71"/>
       <c r="D16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="37" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="40">
+    <row r="17" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="38">
         <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1955,24 +1954,24 @@
         <v>19</v>
       </c>
       <c r="E17" s="7"/>
-      <c r="F17" s="41"/>
-    </row>
-    <row r="18" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="40">
+      <c r="F17" s="39"/>
+    </row>
+    <row r="18" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="38">
         <v>2</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="36"/>
+      <c r="C18" s="34"/>
       <c r="D18" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="41"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="40">
+      <c r="F18" s="39"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="38">
         <v>3</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1983,246 +1982,214 @@
         <v>20</v>
       </c>
       <c r="E19" s="7"/>
-      <c r="F19" s="41"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="40">
+      <c r="F19" s="39"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="38">
         <v>4</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="30"/>
+      <c r="C20" s="28"/>
       <c r="D20" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="37"/>
-      <c r="F20" s="41"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="46">
+      <c r="E20" s="35"/>
+      <c r="F20" s="39"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="44">
         <v>5</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="32"/>
+      <c r="C21" s="30"/>
       <c r="D21" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A22" s="95" t="s">
+      <c r="E21" s="45"/>
+      <c r="F21" s="46"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
-      <c r="F22" s="97"/>
-    </row>
-    <row r="23" spans="1:6" s="2" customFormat="1" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="42" t="s">
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="55"/>
+    </row>
+    <row r="23" spans="1:6" s="2" customFormat="1" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="101"/>
+      <c r="C23" s="67"/>
       <c r="D23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="60" t="s">
+      <c r="E23" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="61"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F23" s="111"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="10">
         <v>1</v>
       </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69"/>
       <c r="D24" s="12"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="63"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E24" s="112"/>
+      <c r="F24" s="113"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="10">
         <v>2</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="51"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="69"/>
       <c r="D25" s="12"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E25" s="112"/>
+      <c r="F25" s="113"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="10">
         <v>3</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="51"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="69"/>
       <c r="D26" s="12"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="43">
+      <c r="E26" s="112"/>
+      <c r="F26" s="113"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="41">
         <v>4</v>
       </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="53"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="104"/>
       <c r="D27" s="14"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="65"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A28" s="95" t="s">
+      <c r="E27" s="114"/>
+      <c r="F27" s="83"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="96"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="96"/>
-      <c r="E28" s="96"/>
-      <c r="F28" s="97"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="98"/>
-      <c r="B29" s="99"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="99"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="100"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="44"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="45"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="44"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="45"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="77"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="65"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A33" s="95" t="s">
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="55"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="100"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="102"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="42"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="43"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="42"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="43"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="81"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="83"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="97"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="79" t="s">
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="55"/>
+    </row>
+    <row r="34" spans="1:6" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="80"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="88" t="s">
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="80"/>
-      <c r="F34" s="89"/>
-    </row>
-    <row r="35" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="81" t="s">
+      <c r="E34" s="85"/>
+      <c r="F34" s="94"/>
+    </row>
+    <row r="35" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="82"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="82" t="s">
+      <c r="B35" s="87"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="82"/>
-      <c r="F35" s="90"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="84" t="s">
+      <c r="E35" s="87"/>
+      <c r="F35" s="95"/>
+    </row>
+    <row r="36" spans="1:6" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="91" t="s">
+      <c r="B36" s="90"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="E36" s="85"/>
-      <c r="F36" s="92"/>
-    </row>
-    <row r="37" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="86" t="s">
+      <c r="E36" s="90"/>
+      <c r="F36" s="97"/>
+    </row>
+    <row r="37" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="87"/>
-      <c r="C37" s="87"/>
-      <c r="D37" s="93" t="s">
+      <c r="B37" s="92"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="87"/>
-      <c r="F37" s="94"/>
-    </row>
-    <row r="38" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="74" t="s">
+      <c r="E37" s="92"/>
+      <c r="F37" s="99"/>
+    </row>
+    <row r="38" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="75"/>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="76"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A11:F11"/>
@@ -2236,6 +2203,38 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.39370078740157483" bottom="0.43307086614173229" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2251,58 +2250,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7414DAC3-4EE8-4239-A8F1-85F6B28A0685}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="9" customWidth="1"/>
-    <col min="2" max="3" width="12.625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="2.625" style="9" customWidth="1"/>
-    <col min="5" max="6" width="12.625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="2.625" style="9" customWidth="1"/>
-    <col min="8" max="9" width="12.625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="9" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" style="9"/>
+    <col min="1" max="1" width="2.6328125" style="9" customWidth="1"/>
+    <col min="2" max="3" width="12.6328125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="2.6328125" style="9" customWidth="1"/>
+    <col min="5" max="6" width="12.6328125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="2.6328125" style="9" customWidth="1"/>
+    <col min="8" max="9" width="12.6328125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="2.6328125" style="9" customWidth="1"/>
+    <col min="11" max="16384" width="8.6328125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:12" ht="56.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="125" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="130"/>
-    </row>
-    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="131" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="127"/>
+    </row>
+    <row r="2" spans="1:12" ht="21.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="128" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="133" t="s">
+      <c r="B2" s="129"/>
+      <c r="C2" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="134"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="136" t="s">
+      <c r="D2" s="131"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="137"/>
-      <c r="H2" s="133" t="s">
+      <c r="G2" s="134"/>
+      <c r="H2" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="134"/>
-      <c r="J2" s="135"/>
-      <c r="L2" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="I2" s="131"/>
+      <c r="J2" s="132"/>
+      <c r="L2" s="48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="15"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -2313,455 +2310,436 @@
       <c r="H3" s="16"/>
       <c r="I3" s="16"/>
       <c r="J3" s="17"/>
-      <c r="L3" s="139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="49" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="15"/>
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="118" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="127" t="s">
+      <c r="C4" s="119"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="127"/>
-      <c r="H4" s="127" t="s">
+      <c r="F4" s="124"/>
+      <c r="H4" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="127"/>
+      <c r="I4" s="124"/>
       <c r="J4" s="17"/>
-      <c r="L4" s="139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="15"/>
-      <c r="B5" s="123"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="124"/>
       <c r="J5" s="17"/>
-      <c r="L5" s="139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L5" s="49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="15"/>
-      <c r="B6" s="123"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="127"/>
-      <c r="F6" s="127"/>
-      <c r="H6" s="127"/>
-      <c r="I6" s="127"/>
+      <c r="B6" s="120"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
       <c r="J6" s="17"/>
     </row>
-    <row r="7" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="15"/>
-      <c r="B7" s="123"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="124"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="124"/>
       <c r="J7" s="17"/>
     </row>
-    <row r="8" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="15"/>
-      <c r="B8" s="123"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
       <c r="J8" s="17"/>
     </row>
-    <row r="9" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="15"/>
-      <c r="B9" s="123"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="20" t="s">
+      <c r="B9" s="120"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="139"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="124"/>
       <c r="J9" s="17"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="15"/>
-      <c r="B10" s="123"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="124"/>
       <c r="J10" s="17"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="15"/>
-      <c r="B11" s="123"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
       <c r="J11" s="17"/>
     </row>
-    <row r="12" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="15"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="139"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
       <c r="J12" s="17"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="15"/>
-      <c r="B13" s="118" t="s">
+      <c r="B13" s="135" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="119"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="120" t="s">
+      <c r="C13" s="136"/>
+      <c r="D13" s="139"/>
+      <c r="E13" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="120"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="120" t="s">
+      <c r="F13" s="137"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="120"/>
+      <c r="I13" s="137"/>
       <c r="J13" s="17"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="15"/>
+      <c r="D14" s="140"/>
       <c r="J14" s="17"/>
     </row>
-    <row r="15" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="15"/>
-      <c r="B15" s="121" t="s">
+      <c r="B15" s="118" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="122"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="127" t="s">
+      <c r="C15" s="119"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="127"/>
-      <c r="H15" s="127" t="s">
+      <c r="F15" s="124"/>
+      <c r="H15" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="I15" s="127"/>
+      <c r="I15" s="124"/>
       <c r="J15" s="17"/>
     </row>
-    <row r="16" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="15"/>
-      <c r="B16" s="123"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="121"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="124"/>
       <c r="J16" s="17"/>
     </row>
-    <row r="17" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="15"/>
-      <c r="B17" s="123"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
+      <c r="B17" s="120"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="124"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="124"/>
       <c r="J17" s="17"/>
     </row>
-    <row r="18" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="15"/>
-      <c r="B18" s="123"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
+      <c r="B18" s="120"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
       <c r="J18" s="17"/>
     </row>
-    <row r="19" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="15"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="124"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="124"/>
       <c r="J19" s="17"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="15"/>
-      <c r="B20" s="123"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="20" t="s">
+      <c r="B20" s="120"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H20" s="127"/>
-      <c r="I20" s="127"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="124"/>
       <c r="J20" s="17"/>
     </row>
-    <row r="21" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="15"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="127"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="139"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="124"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="124"/>
+      <c r="I21" s="124"/>
       <c r="J21" s="17"/>
     </row>
-    <row r="22" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="15"/>
-      <c r="B22" s="123"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="127"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="121"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="124"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="124"/>
+      <c r="I22" s="124"/>
       <c r="J22" s="17"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="15"/>
-      <c r="B23" s="125"/>
-      <c r="C23" s="126"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="139"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="124"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="124"/>
+      <c r="I23" s="124"/>
       <c r="J23" s="17"/>
     </row>
-    <row r="24" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="15"/>
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="120"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="120" t="s">
+      <c r="C24" s="137"/>
+      <c r="D24" s="139"/>
+      <c r="E24" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="120"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="120" t="s">
+      <c r="F24" s="137"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="137" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="120"/>
+      <c r="I24" s="137"/>
       <c r="J24" s="17"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="15"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="22" t="s">
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
       <c r="J25" s="17"/>
     </row>
-    <row r="26" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="15"/>
-      <c r="B26" s="121" t="s">
+      <c r="B26" s="118" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="122"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="127" t="s">
+      <c r="C26" s="119"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="127"/>
-      <c r="H26" s="127" t="s">
+      <c r="F26" s="124"/>
+      <c r="H26" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="I26" s="127"/>
+      <c r="I26" s="124"/>
       <c r="J26" s="17"/>
     </row>
-    <row r="27" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="15"/>
-      <c r="B27" s="123"/>
-      <c r="C27" s="124"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="127"/>
-      <c r="F27" s="127"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="127"/>
+      <c r="B27" s="120"/>
+      <c r="C27" s="121"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
+      <c r="H27" s="124"/>
+      <c r="I27" s="124"/>
       <c r="J27" s="17"/>
     </row>
-    <row r="28" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="15"/>
-      <c r="B28" s="123"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="127"/>
-      <c r="F28" s="127"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="127"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="121"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="124"/>
+      <c r="H28" s="124"/>
+      <c r="I28" s="124"/>
       <c r="J28" s="17"/>
     </row>
-    <row r="29" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="15"/>
-      <c r="B29" s="123"/>
-      <c r="C29" s="124"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
+      <c r="B29" s="120"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="124"/>
+      <c r="F29" s="124"/>
+      <c r="H29" s="124"/>
+      <c r="I29" s="124"/>
       <c r="J29" s="17"/>
     </row>
-    <row r="30" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="15"/>
-      <c r="B30" s="123"/>
-      <c r="C30" s="124"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="127"/>
-      <c r="F30" s="127"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="127"/>
+      <c r="B30" s="120"/>
+      <c r="C30" s="121"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="124"/>
+      <c r="H30" s="124"/>
+      <c r="I30" s="124"/>
       <c r="J30" s="17"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="15"/>
-      <c r="B31" s="123"/>
-      <c r="C31" s="124"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="127"/>
-      <c r="F31" s="127"/>
-      <c r="G31" s="20" t="s">
+      <c r="B31" s="120"/>
+      <c r="C31" s="121"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="124"/>
+      <c r="G31" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H31" s="127"/>
-      <c r="I31" s="127"/>
+      <c r="H31" s="124"/>
+      <c r="I31" s="124"/>
       <c r="J31" s="17"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="15"/>
-      <c r="B32" s="123"/>
-      <c r="C32" s="124"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="127"/>
-      <c r="F32" s="127"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="127"/>
+      <c r="B32" s="120"/>
+      <c r="C32" s="121"/>
+      <c r="D32" s="139"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="124"/>
+      <c r="I32" s="124"/>
       <c r="J32" s="17"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="15"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
+      <c r="B33" s="120"/>
+      <c r="C33" s="121"/>
+      <c r="D33" s="139"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="124"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="124"/>
+      <c r="I33" s="124"/>
       <c r="J33" s="17"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="15"/>
-      <c r="B34" s="125"/>
-      <c r="C34" s="126"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="127"/>
+      <c r="B34" s="122"/>
+      <c r="C34" s="123"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="124"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="124"/>
+      <c r="I34" s="124"/>
       <c r="J34" s="17"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="15"/>
-      <c r="B35" s="118" t="s">
+      <c r="B35" s="135" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="119"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="120" t="s">
+      <c r="C35" s="136"/>
+      <c r="D35" s="139"/>
+      <c r="E35" s="137" t="s">
         <v>47</v>
       </c>
-      <c r="F35" s="120"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="120" t="s">
+      <c r="F35" s="137"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="137" t="s">
         <v>48</v>
       </c>
-      <c r="I35" s="120"/>
+      <c r="I35" s="137"/>
       <c r="J35" s="17"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="23"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="25"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="21"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B4:C12"/>
-    <mergeCell ref="E4:F12"/>
-    <mergeCell ref="H4:I12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="B15:C23"/>
-    <mergeCell ref="E15:F23"/>
-    <mergeCell ref="H15:I23"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="H35:I35"/>
@@ -2771,6 +2749,20 @@
     <mergeCell ref="B26:C34"/>
     <mergeCell ref="E26:F34"/>
     <mergeCell ref="H26:I34"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B15:C23"/>
+    <mergeCell ref="E15:F23"/>
+    <mergeCell ref="H15:I23"/>
+    <mergeCell ref="B4:C12"/>
+    <mergeCell ref="E4:F12"/>
+    <mergeCell ref="H4:I12"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.51181102362204722" bottom="0.31496062992125984" header="0.51181102362204722" footer="0.51181102362204722"/>
